--- a/artfynd/A 15765-2020 artfynd.xlsx
+++ b/artfynd/A 15765-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15765-2020 artfynd.xlsx
+++ b/artfynd/A 15765-2020 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>117500352</v>
       </c>
       <c r="B3" t="n">
-        <v>56718</v>
+        <v>56719</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 15765-2020 artfynd.xlsx
+++ b/artfynd/A 15765-2020 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>121316540</v>
       </c>
       <c r="B4" t="n">
-        <v>56401</v>
+        <v>56404</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 15765-2020 artfynd.xlsx
+++ b/artfynd/A 15765-2020 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>121316540</v>
       </c>
       <c r="B4" t="n">
-        <v>56404</v>
+        <v>56407</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 15765-2020 artfynd.xlsx
+++ b/artfynd/A 15765-2020 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>121316540</v>
       </c>
       <c r="B4" t="n">
-        <v>56407</v>
+        <v>56408</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 15765-2020 artfynd.xlsx
+++ b/artfynd/A 15765-2020 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>121316540</v>
       </c>
       <c r="B4" t="n">
-        <v>56408</v>
+        <v>56409</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 15765-2020 artfynd.xlsx
+++ b/artfynd/A 15765-2020 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>121316540</v>
       </c>
       <c r="B4" t="n">
-        <v>56409</v>
+        <v>56410</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 15765-2020 artfynd.xlsx
+++ b/artfynd/A 15765-2020 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>117500352</v>
       </c>
       <c r="B3" t="n">
-        <v>56719</v>
+        <v>56907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 15765-2020 artfynd.xlsx
+++ b/artfynd/A 15765-2020 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>117500352</v>
       </c>
       <c r="B3" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 15765-2020 artfynd.xlsx
+++ b/artfynd/A 15765-2020 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>117500352</v>
       </c>
       <c r="B3" t="n">
-        <v>56910</v>
+        <v>56916</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 15765-2020 artfynd.xlsx
+++ b/artfynd/A 15765-2020 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>117500352</v>
       </c>
       <c r="B3" t="n">
-        <v>56916</v>
+        <v>56919</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
